--- a/artfynd/A 28997-2025 artfynd.xlsx
+++ b/artfynd/A 28997-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1833,6 +1833,297 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127691952</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80149</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tjålmsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>600963</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7033595</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127691953</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90365</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tjålmsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>600963</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7033595</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127691950</v>
+      </c>
+      <c r="B14" t="n">
+        <v>96573</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tjålmsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>600898</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7033708</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28997-2025 artfynd.xlsx
+++ b/artfynd/A 28997-2025 artfynd.xlsx
@@ -1838,7 +1838,7 @@
         <v>127691952</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>80151</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>127691953</v>
       </c>
       <c r="B13" t="n">
-        <v>90365</v>
+        <v>90367</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>127691950</v>
       </c>
       <c r="B14" t="n">
-        <v>96573</v>
+        <v>96575</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 28997-2025 artfynd.xlsx
+++ b/artfynd/A 28997-2025 artfynd.xlsx
@@ -1935,7 +1935,7 @@
         <v>127691953</v>
       </c>
       <c r="B13" t="n">
-        <v>90367</v>
+        <v>90373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>127691950</v>
       </c>
       <c r="B14" t="n">
-        <v>96575</v>
+        <v>96581</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 28997-2025 artfynd.xlsx
+++ b/artfynd/A 28997-2025 artfynd.xlsx
@@ -1838,7 +1838,7 @@
         <v>127691952</v>
       </c>
       <c r="B12" t="n">
-        <v>80151</v>
+        <v>80154</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>127691953</v>
       </c>
       <c r="B13" t="n">
-        <v>90373</v>
+        <v>90376</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>127691950</v>
       </c>
       <c r="B14" t="n">
-        <v>96581</v>
+        <v>96584</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 28997-2025 artfynd.xlsx
+++ b/artfynd/A 28997-2025 artfynd.xlsx
@@ -1838,7 +1838,7 @@
         <v>127691952</v>
       </c>
       <c r="B12" t="n">
-        <v>80154</v>
+        <v>80160</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>127691953</v>
       </c>
       <c r="B13" t="n">
-        <v>90376</v>
+        <v>90384</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>127691950</v>
       </c>
       <c r="B14" t="n">
-        <v>96584</v>
+        <v>96592</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 28997-2025 artfynd.xlsx
+++ b/artfynd/A 28997-2025 artfynd.xlsx
@@ -1935,7 +1935,7 @@
         <v>127691953</v>
       </c>
       <c r="B13" t="n">
-        <v>90384</v>
+        <v>90385</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>127691950</v>
       </c>
       <c r="B14" t="n">
-        <v>96592</v>
+        <v>96593</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 28997-2025 artfynd.xlsx
+++ b/artfynd/A 28997-2025 artfynd.xlsx
@@ -1935,7 +1935,7 @@
         <v>127691953</v>
       </c>
       <c r="B13" t="n">
-        <v>90385</v>
+        <v>90386</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>127691950</v>
       </c>
       <c r="B14" t="n">
-        <v>96593</v>
+        <v>96594</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 28997-2025 artfynd.xlsx
+++ b/artfynd/A 28997-2025 artfynd.xlsx
@@ -1935,7 +1935,7 @@
         <v>127691953</v>
       </c>
       <c r="B13" t="n">
-        <v>90386</v>
+        <v>90387</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>127691950</v>
       </c>
       <c r="B14" t="n">
-        <v>96594</v>
+        <v>96595</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 28997-2025 artfynd.xlsx
+++ b/artfynd/A 28997-2025 artfynd.xlsx
@@ -1838,7 +1838,7 @@
         <v>127691952</v>
       </c>
       <c r="B12" t="n">
-        <v>80160</v>
+        <v>80163</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>127691953</v>
       </c>
       <c r="B13" t="n">
-        <v>90387</v>
+        <v>90393</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>127691950</v>
       </c>
       <c r="B14" t="n">
-        <v>96595</v>
+        <v>96603</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 28997-2025 artfynd.xlsx
+++ b/artfynd/A 28997-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1867414</v>
+        <v>89570</v>
       </c>
       <c r="B2" t="n">
-        <v>77595</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6450</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601090.160917229</v>
+        <v>601035</v>
       </c>
       <c r="R2" t="n">
-        <v>7033549.114117603</v>
+        <v>7033581</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,26 +743,11 @@
           <t>2007-10-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2007-10-05</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Lav och mossrikt block</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -776,6 +756,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>tallåga</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97808</v>
+        <v>97805</v>
       </c>
       <c r="B3" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601007.6817670562</v>
+        <v>601011</v>
       </c>
       <c r="R3" t="n">
-        <v>7033574.296026875</v>
+        <v>7033610</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -865,19 +845,9 @@
           <t>2007-10-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2007-10-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,22 +872,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Hans Sundström, Sofia Lundell</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97805</v>
+        <v>97807</v>
       </c>
       <c r="B4" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601011.4820222849</v>
+        <v>601005</v>
       </c>
       <c r="R4" t="n">
-        <v>7033610.272058626</v>
+        <v>7033595</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -982,19 +947,14 @@
           <t>2007-10-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2007-10-05</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Grov tallåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,6 +965,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1026,15 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97807</v>
+        <v>97808</v>
       </c>
       <c r="B5" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601004.7751419622</v>
+        <v>601008</v>
       </c>
       <c r="R5" t="n">
-        <v>7033595.269630786</v>
+        <v>7033574</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,26 +1059,11 @@
           <t>2007-10-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2007-10-05</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Grov tallåga</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1127,11 +1072,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -1146,22 +1086,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hans Sundström, Sofia Lundell</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1829812</v>
+        <v>127691953</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,37 +1104,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjålmsjömyran, Ång</t>
+          <t>Tjålmsjön, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601095.0362805742</v>
+        <v>600963</v>
       </c>
       <c r="R6" t="n">
-        <v>7033551.061094839</v>
+        <v>7033595</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,22 +1158,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2007-10-05</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2007-10-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,65 +1178,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Andreas Karlberg</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hans Sundström, Sofia Lundell</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1829809</v>
+        <v>127691950</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tjålmsjömyran, Ång</t>
+          <t>Tjålmsjön, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601033.6724682851</v>
+        <v>600898</v>
       </c>
       <c r="R7" t="n">
-        <v>7033575.565440626</v>
+        <v>7033708</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1335,22 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2007-10-05</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2007-10-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,49 +1275,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Andreas Karlberg</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hans Sundström, Sofia Lundell</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89570</v>
+        <v>1829809</v>
       </c>
       <c r="B8" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601034.8619026527</v>
+        <v>601034</v>
       </c>
       <c r="R8" t="n">
-        <v>7033580.533247923</v>
+        <v>7033576</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1450,21 +1355,11 @@
           <t>2007-10-05</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2007-10-05</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1473,11 +1368,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>tallåga</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1494,37 +1384,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97806</v>
+        <v>1829810</v>
       </c>
       <c r="B9" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601103.1162464693</v>
+        <v>601035</v>
       </c>
       <c r="R9" t="n">
-        <v>7033565.210952352</v>
+        <v>7033581</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1567,21 +1452,11 @@
           <t>2007-10-05</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2007-10-05</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1590,11 +1465,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1611,37 +1481,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1829810</v>
+        <v>2009200</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1651,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601034.8619026527</v>
+        <v>601011</v>
       </c>
       <c r="R10" t="n">
-        <v>7033580.533247923</v>
+        <v>7033610</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1684,19 +1549,9 @@
           <t>2007-10-05</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2007-10-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,15 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2009200</v>
+        <v>127691952</v>
       </c>
       <c r="B11" t="n">
-        <v>78595</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,17 +1609,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tjålmsjömyran, Ång</t>
+          <t>Tjålmsjön, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601011.4820222849</v>
+        <v>600963</v>
       </c>
       <c r="R11" t="n">
-        <v>7033610.272058626</v>
+        <v>7033595</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1793,22 +1643,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2007-10-05</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2007-10-05</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,60 +1663,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Andreas Karlberg</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hans Sundström, Sofia Lundell</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127691952</v>
+        <v>97806</v>
       </c>
       <c r="B12" t="n">
-        <v>80163</v>
+        <v>78993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tjålmsjön, Ång</t>
+          <t>Tjålmsjömyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600963</v>
+        <v>601103</v>
       </c>
       <c r="R12" t="n">
-        <v>7033595</v>
+        <v>7033565</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1900,12 +1740,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2007-10-05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2007-10-05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,64 +1756,69 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Andreas Karlberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Hans Sundström, Sofia Lundell</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127691953</v>
+        <v>1829812</v>
       </c>
       <c r="B13" t="n">
-        <v>90393</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tjålmsjön, Ång</t>
+          <t>Tjålmsjömyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600963</v>
+        <v>601095</v>
       </c>
       <c r="R13" t="n">
-        <v>7033595</v>
+        <v>7033551</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1997,12 +1842,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2007-10-05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2007-10-05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,60 +1862,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Andreas Karlberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Hans Sundström, Sofia Lundell</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127691950</v>
+        <v>1867414</v>
       </c>
       <c r="B14" t="n">
-        <v>96603</v>
+        <v>79413</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2869</v>
+        <v>6450</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tjålmsjön, Ång</t>
+          <t>Tjålmsjömyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600898</v>
+        <v>601090</v>
       </c>
       <c r="R14" t="n">
-        <v>7033708</v>
+        <v>7033549</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2094,12 +1939,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2007-10-05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2007-10-05</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Lav och mossrikt block</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,15 +1964,117 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Andreas Karlberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Hans Sundström, Sofia Lundell</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6692152</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tjålmsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>601095</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7033551</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2007-10-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2007-10-05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Andreas Karlberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Hans Sundström, Sofia Lundell</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28997-2025 artfynd.xlsx
+++ b/artfynd/A 28997-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89570</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97805</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97806</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97807</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97808</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127691953</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127691950</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,6 +1523,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1829809</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1580,6 +1625,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1829810</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1677,6 +1727,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1829812</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1779,6 +1834,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1867414</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1876,6 +1936,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2009200</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1973,6 +2038,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127691952</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2075,8 +2145,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6692152</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>